--- a/dietaryindex_SERVING_SIZE_DEFINITION.xlsx
+++ b/dietaryindex_SERVING_SIZE_DEFINITION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11018"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Library/Mobile Documents/com~apple~CloudDocs/Desktop/Emory University - Ph.D./dietaryindex_package/dietaryindex/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Desktop/Emory University - Ph.D./dietaryindex_package/dietaryindex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FB4FF2-0C37-D940-BBFE-C7FA75AB39F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880415D0-DDE2-994B-B25E-0E44ABD23BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11440" yWindow="500" windowWidth="26780" windowHeight="19460" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="500" windowWidth="26800" windowHeight="19460" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NHANES_HEI2020" sheetId="18" r:id="rId1"/>
@@ -21,22 +21,23 @@
     <sheet name="NHANES_MED" sheetId="7" r:id="rId6"/>
     <sheet name="NHANES_MEDI" sheetId="6" r:id="rId7"/>
     <sheet name="NHANES_DII" sheetId="20" r:id="rId8"/>
-    <sheet name="ASA24_HEI2020" sheetId="36" r:id="rId9"/>
-    <sheet name="ASA24_HEI2015" sheetId="21" r:id="rId10"/>
-    <sheet name="ASA24_AHEI-2010" sheetId="22" r:id="rId11"/>
-    <sheet name="ASA24_DASH" sheetId="23" r:id="rId12"/>
-    <sheet name="ASA24_MED" sheetId="24" r:id="rId13"/>
-    <sheet name="ASA24_DII" sheetId="25" r:id="rId14"/>
-    <sheet name="DHQ3_HEI2015" sheetId="26" r:id="rId15"/>
-    <sheet name="DHQ3_AHEI-2010" sheetId="27" r:id="rId16"/>
-    <sheet name="DHQ3_DASH" sheetId="28" r:id="rId17"/>
-    <sheet name="DHQ3_MED" sheetId="29" r:id="rId18"/>
-    <sheet name="BLOCK_FFQ_HEI2015" sheetId="30" r:id="rId19"/>
-    <sheet name="BLOCK_FFQ_AHEI-2010" sheetId="31" r:id="rId20"/>
-    <sheet name="BLOCK_FFQ_AHEIP" sheetId="32" r:id="rId21"/>
-    <sheet name="BLOCK_FFQ_DASH" sheetId="33" r:id="rId22"/>
-    <sheet name="BLOCK_FFQ_MED" sheetId="34" r:id="rId23"/>
-    <sheet name="BLOCK_FFQ_DII" sheetId="35" r:id="rId24"/>
+    <sheet name="NHANES_DI-GM" sheetId="37" r:id="rId9"/>
+    <sheet name="ASA24_HEI2020" sheetId="36" r:id="rId10"/>
+    <sheet name="ASA24_HEI2015" sheetId="21" r:id="rId11"/>
+    <sheet name="ASA24_AHEI-2010" sheetId="22" r:id="rId12"/>
+    <sheet name="ASA24_DASH" sheetId="23" r:id="rId13"/>
+    <sheet name="ASA24_MED" sheetId="24" r:id="rId14"/>
+    <sheet name="ASA24_DII" sheetId="25" r:id="rId15"/>
+    <sheet name="DHQ3_HEI2015" sheetId="26" r:id="rId16"/>
+    <sheet name="DHQ3_AHEI-2010" sheetId="27" r:id="rId17"/>
+    <sheet name="DHQ3_DASH" sheetId="28" r:id="rId18"/>
+    <sheet name="DHQ3_MED" sheetId="29" r:id="rId19"/>
+    <sheet name="BLOCK_FFQ_HEI2015" sheetId="30" r:id="rId20"/>
+    <sheet name="BLOCK_FFQ_AHEI-2010" sheetId="31" r:id="rId21"/>
+    <sheet name="BLOCK_FFQ_AHEIP" sheetId="32" r:id="rId22"/>
+    <sheet name="BLOCK_FFQ_DASH" sheetId="33" r:id="rId23"/>
+    <sheet name="BLOCK_FFQ_MED" sheetId="34" r:id="rId24"/>
+    <sheet name="BLOCK_FFQ_DII" sheetId="35" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">NHANES_DII!$A$2:$F$47</definedName>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="542">
   <si>
     <t>Component</t>
   </si>
@@ -1704,12 +1705,160 @@
   <si>
     <t>Calculated by using Database of Flavonoid Values for USDA Food Codes (Flavonoid Database), available for NHANES 2007-2010 and 2017-2018</t>
   </si>
+  <si>
+    <t>Included Foods within the Component</t>
+  </si>
+  <si>
+    <t>Dietary Index for Gut Microbiota (DI-GM)</t>
+  </si>
+  <si>
+    <t>Avocados</t>
+  </si>
+  <si>
+    <t>Broccoli</t>
+  </si>
+  <si>
+    <t>Chickpea</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Cranberries</t>
+  </si>
+  <si>
+    <t>Fermented dairy</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Green tea</t>
+  </si>
+  <si>
+    <t>Soybean</t>
+  </si>
+  <si>
+    <t>Soy products–-Soy milk, Tofu</t>
+  </si>
+  <si>
+    <t>Grains defined as whole grains,
+containing the entire grain kernel—the
+bran, germ, and endosperm</t>
+  </si>
+  <si>
+    <t>High-fat diet (% energy)</t>
+  </si>
+  <si>
+    <t>Processed meat</t>
+  </si>
+  <si>
+    <t>Frankfurters, sausages, corned beef, and
+luncheon meat that are made from beef,
+pork, or poultry</t>
+  </si>
+  <si>
+    <t>Red meat</t>
+  </si>
+  <si>
+    <t>Beef, veal, pork, lamb, and game meat;
+excludes organ meat and cured meat</t>
+  </si>
+  <si>
+    <t>Refined grains</t>
+  </si>
+  <si>
+    <t>Refined grains that do not contain all of
+the components of the entire grain kernel</t>
+  </si>
+  <si>
+    <t>Food code</t>
+  </si>
+  <si>
+    <t>gram</t>
+  </si>
+  <si>
+    <t>c(72103000, 72103030, 72201100, 72201190, 72201211, 72201212, 72201220, 72201221, 72201222, 72201223, 72201224, 72201226, 72201227, 72203000, 72203070)</t>
+  </si>
+  <si>
+    <t>c(41301990, 41302010, 41302020, 41302040, 41302080, 41302110)</t>
+  </si>
+  <si>
+    <t>c(92100000, 92100500, 92101000, 92101500, 92101600, 92101610, 92101630, 92101700, 92101800, 92101810, 
+  92101820, 92101850, 92101851, 92101900, 92101901, 92101903, 92101904, 92101905, 92101906, 92101910, 
+  92101911, 92101913, 92101917, 92101918, 92101919, 92101920, 92101921, 92101923, 92101925, 92101926, 
+  92101928, 92101930, 92101931, 92101933, 92101935, 92101936, 92101938, 92101950, 92101955, 92101960, 
+  92101965, 92101970, 92101975, 92102000, 92102010, 92102020, 92102030, 92102040, 92102050, 92102060, 
+  92102070, 92102080, 92102090, 92102100, 92102110, 92102400, 92102401, 92102450, 92102500, 92102501, 
+  92102502, 92102503, 92102504, 92102505, 92102510, 92102511, 92102512, 92102513, 92102514, 92102515, 
+  92102600, 92102601, 92102602, 92102610, 92102611, 92102612, 92103000, 92104000, 92111000, 92111010, 
+  92114000, 92121000, 92121001, 92121010, 92121020, 92121030, 92121040, 92121041, 92121050, 92130000, 
+  92130001, 92130005, 92130006, 92130010, 92130011, 92130020, 92130021, 92130030, 92130031, 92152000, 
+  92152010, 92161000, 92161001, 92161002, 92162000, 92162001, 92162002, 92171000, 92171010, 92201010)</t>
+  </si>
+  <si>
+    <t>c(62109100, 63207010, 63207110)</t>
+  </si>
+  <si>
+    <t>Yogurt, cheese, kefir, sour cream, buttermilk</t>
+  </si>
+  <si>
+    <t>c(11400000, 11400010, 11410000, 11411010, 11411100, 11411200, 11411300, 11411390, 11411400, 11411410,
+  11411420, 11430000, 11431000, 11432000, 11433000, 11433990, 11434000, 11434010, 11434020, 11434090,
+  11434100, 11434200, 11434300, 11435000, 11435010, 11435020, 11435030, 11435100, 11436000, 11446000,
+  11480010, 11480020, 11480030, 11480040, 42401100, 67250100, 67250150, 67404070, 67404300, 67404500,
+  67408500, 67413700, 67430500, 14010000, 14101010, 14102010, 14103010, 14103020, 14104100, 14104110,
+  14104115, 14104200, 14104250, 14104400, 14104600, 14104700, 14105010, 14105200, 14106010, 14106200,
+  14106500, 14107010, 14107030, 14107040, 14107060, 14107200, 14107250, 14108010, 14108015, 14108020,
+  14108060, 14108200, 14108400, 14108420, 14109010, 14109020, 14109030, 14109040, 14110010, 14120010,
+  14120020, 14131000, 14200100, 14201010, 14201200, 14201500, 14202010, 14202020, 14203010, 14203020,
+  14203510, 14204010, 14204020, 14206010, 14207010, 14410100, 14410110, 14410120, 14410130, 14410210,
+  14410330, 14410500, 14410600, 14410620, 14420100, 14420160, 14420300, 14502000, 14610200, 14610210,
+  14610250, 14610520, 11115400, 12310100, 12310350, 12310370, 12320100, 11115000, 11115100, 11115200,
+  11115300)</t>
+  </si>
+  <si>
+    <t>c(11320000, 11320100, 11320200, 11321000, 11321100, 11321200, 41107010, 41410010)</t>
+  </si>
+  <si>
+    <t>oz</t>
+  </si>
+  <si>
+    <t>DR1T_G_REFINED</t>
+  </si>
+  <si>
+    <t>DR1T_PF_MEAT</t>
+  </si>
+  <si>
+    <t>% energy</t>
+  </si>
+  <si>
+    <t>c(92303010, 92303100, 92305900, 92305910, 92305920, 92308500, 92308510, 92308520, 92308530, 92308540, 92308550, 92309500, 92309510, 92309520)</t>
+  </si>
+  <si>
+    <t>use all the food codes on the left side</t>
+  </si>
+  <si>
+    <t>DR1IFIBE</t>
+  </si>
+  <si>
+    <t>(DR1ITFAT * 9/DR1IKCAL) * 100</t>
+  </si>
+  <si>
+    <t>DR1I_PF_CUREDMEAT</t>
+  </si>
+  <si>
+    <t>Reference:</t>
+  </si>
+  <si>
+    <t>Kase BE, Liese AD, Zhang J, Murphy EA, Zhao L, Steck SE. The Development and Evaluation of a Literature-Based Dietary Index for Gut Microbiota. Nutrients. 2024;16(7):1045. Published 2024 Apr 3. doi:10.3390/nu16071045</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1781,6 +1930,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1822,7 +1992,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1874,6 +2044,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1891,6 +2071,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2470,14 +2654,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2507,7 +2691,7 @@
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="25" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2527,7 +2711,7 @@
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="21"/>
+      <c r="F4" s="25"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -2545,7 +2729,7 @@
       <c r="E5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="21"/>
+      <c r="F5" s="25"/>
     </row>
     <row r="6" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -2563,7 +2747,7 @@
       <c r="E6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="21"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -2581,7 +2765,7 @@
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="21"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -2599,7 +2783,7 @@
       <c r="E8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="21"/>
+      <c r="F8" s="25"/>
     </row>
     <row r="9" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -2617,7 +2801,7 @@
       <c r="E9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="21"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -2635,7 +2819,7 @@
       <c r="E10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="21"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -2653,7 +2837,7 @@
       <c r="E11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="21"/>
+      <c r="F11" s="25"/>
     </row>
     <row r="12" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -2671,7 +2855,7 @@
       <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="21"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
@@ -2681,7 +2865,7 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="21"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -2699,7 +2883,7 @@
       <c r="E14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="21"/>
+      <c r="F14" s="25"/>
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -2717,7 +2901,7 @@
       <c r="E15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="21"/>
+      <c r="F15" s="25"/>
     </row>
     <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -2735,7 +2919,7 @@
       <c r="E16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="21"/>
+      <c r="F16" s="25"/>
     </row>
     <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -2753,7 +2937,7 @@
       <c r="E17" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="21"/>
+      <c r="F17" s="25"/>
     </row>
     <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="8"/>
@@ -2781,6 +2965,330 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21D5B17-DF60-214C-A0BB-8AA9F6288E63}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
+        <v>484</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25"/>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25"/>
+    </row>
+    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="25"/>
+    </row>
+    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="25"/>
+    </row>
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="25"/>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25"/>
+    </row>
+    <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="25"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="25"/>
+    </row>
+    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="25"/>
+    </row>
+    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="25"/>
+    </row>
+    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="25"/>
+    </row>
+    <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="25"/>
+    </row>
+    <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="F3:F17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4165A63-3924-5045-B08F-E7F2ABCF1698}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2794,14 +3302,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2831,7 +3339,7 @@
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="25" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2851,7 +3359,7 @@
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="21"/>
+      <c r="F4" s="25"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -2869,7 +3377,7 @@
       <c r="E5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="21"/>
+      <c r="F5" s="25"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -2887,7 +3395,7 @@
       <c r="E6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="21"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -2905,7 +3413,7 @@
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="21"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -2923,7 +3431,7 @@
       <c r="E8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="21"/>
+      <c r="F8" s="25"/>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -2941,7 +3449,7 @@
       <c r="E9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="21"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -2959,7 +3467,7 @@
       <c r="E10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="21"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -2977,7 +3485,7 @@
       <c r="E11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="21"/>
+      <c r="F11" s="25"/>
     </row>
     <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -2995,7 +3503,7 @@
       <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="21"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
@@ -3005,7 +3513,7 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="21"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -3023,7 +3531,7 @@
       <c r="E14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="21"/>
+      <c r="F14" s="25"/>
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -3041,7 +3549,7 @@
       <c r="E15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="21"/>
+      <c r="F15" s="25"/>
     </row>
     <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -3059,7 +3567,7 @@
       <c r="E16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="21"/>
+      <c r="F16" s="25"/>
     </row>
     <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -3077,7 +3585,7 @@
       <c r="E17" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="21"/>
+      <c r="F17" s="25"/>
     </row>
     <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="8"/>
@@ -3104,7 +3612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA2095F6-DF52-CF40-903A-4F593F172A76}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3119,13 +3627,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -3168,7 +3676,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3189,7 +3697,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="23"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -3208,7 +3716,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="7"/>
-      <c r="G5" s="23"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -3227,7 +3735,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="7"/>
-      <c r="G6" s="23"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -3246,7 +3754,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="7"/>
-      <c r="G7" s="23"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -3265,7 +3773,7 @@
         <v>37</v>
       </c>
       <c r="F8" s="7"/>
-      <c r="G8" s="23"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -3284,7 +3792,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="7"/>
-      <c r="G9" s="23"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -3303,7 +3811,7 @@
         <v>36</v>
       </c>
       <c r="F10" s="7"/>
-      <c r="G10" s="23"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -3314,7 +3822,7 @@
       <c r="F11" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="G11" s="23"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -3333,7 +3841,7 @@
         <v>170</v>
       </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="23"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -3352,7 +3860,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="7"/>
-      <c r="G13" s="23"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -3364,8 +3872,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="28" t="s">
         <v>485</v>
       </c>
     </row>
@@ -3380,7 +3888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBDA4B05-327F-9E4B-9EF4-3FD2F5F781E6}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3393,13 +3901,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -3438,7 +3946,7 @@
       <c r="E3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3458,7 +3966,7 @@
       <c r="E4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -3476,7 +3984,7 @@
       <c r="E5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -3494,7 +4002,7 @@
       <c r="E6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="320" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -3512,7 +4020,7 @@
       <c r="E7" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -3527,7 +4035,7 @@
       <c r="E8" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -3545,7 +4053,7 @@
       <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -3563,7 +4071,7 @@
       <c r="E10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -3574,13 +4082,13 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="29" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="28" t="s">
         <v>486</v>
       </c>
     </row>
@@ -3599,7 +4107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077FE58D-9868-7440-9DD9-B284E00EA402}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3612,13 +4120,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -3657,7 +4165,7 @@
       <c r="E3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3677,7 +4185,7 @@
       <c r="E4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -3695,7 +4203,7 @@
       <c r="E5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -3713,7 +4221,7 @@
       <c r="E6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -3731,7 +4239,7 @@
       <c r="E7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -3749,7 +4257,7 @@
       <c r="E8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -3767,7 +4275,7 @@
       <c r="E9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -3785,7 +4293,7 @@
       <c r="E10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -3803,7 +4311,7 @@
       <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -3819,8 +4327,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="28" t="s">
         <v>486</v>
       </c>
     </row>
@@ -3835,7 +4343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A9F33AE-4988-6742-81A0-43A9D33AA59A}">
   <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3849,13 +4357,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -3891,7 +4399,7 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3908,7 +4416,7 @@
       <c r="D4" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -3923,7 +4431,7 @@
       <c r="D5" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -3938,7 +4446,7 @@
       <c r="D6" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -3953,7 +4461,7 @@
       <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -3968,7 +4476,7 @@
       <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -3983,7 +4491,7 @@
       <c r="D9" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -3998,7 +4506,7 @@
       <c r="D10" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -4014,7 +4522,7 @@
       <c r="E11" t="s">
         <v>325</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -4029,7 +4537,7 @@
       <c r="D12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="23"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -4044,7 +4552,7 @@
       <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="23"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -4059,7 +4567,7 @@
       <c r="D14" t="s">
         <v>120</v>
       </c>
-      <c r="F14" s="23"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -4075,7 +4583,7 @@
       <c r="E15" t="s">
         <v>325</v>
       </c>
-      <c r="F15" s="23"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -4091,7 +4599,7 @@
       <c r="E16" t="s">
         <v>325</v>
       </c>
-      <c r="F16" s="23"/>
+      <c r="F16" s="27"/>
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -4106,7 +4614,7 @@
       <c r="D17" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="23"/>
+      <c r="F17" s="27"/>
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
@@ -4121,7 +4629,7 @@
       <c r="D18" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="23"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
@@ -4136,7 +4644,7 @@
       <c r="D19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="23"/>
+      <c r="F19" s="27"/>
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
@@ -4151,7 +4659,7 @@
       <c r="D20" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="23"/>
+      <c r="F20" s="27"/>
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
@@ -4166,7 +4674,7 @@
       <c r="D21" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="23"/>
+      <c r="F21" s="27"/>
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
@@ -4181,7 +4689,7 @@
       <c r="D22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="23"/>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -4197,7 +4705,7 @@
       <c r="E23" t="s">
         <v>325</v>
       </c>
-      <c r="F23" s="23"/>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
@@ -4212,7 +4720,7 @@
       <c r="D24" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="23"/>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
@@ -4227,7 +4735,7 @@
       <c r="D25" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="23"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
@@ -4242,7 +4750,7 @@
       <c r="D26" t="s">
         <v>121</v>
       </c>
-      <c r="F26" s="23"/>
+      <c r="F26" s="27"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
@@ -4258,7 +4766,7 @@
       <c r="E27" t="s">
         <v>325</v>
       </c>
-      <c r="F27" s="23"/>
+      <c r="F27" s="27"/>
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
@@ -4273,7 +4781,7 @@
       <c r="D28" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="23"/>
+      <c r="F28" s="27"/>
     </row>
     <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -4288,7 +4796,7 @@
       <c r="D29" t="s">
         <v>120</v>
       </c>
-      <c r="F29" s="23"/>
+      <c r="F29" s="27"/>
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
@@ -4303,7 +4811,7 @@
       <c r="D30" t="s">
         <v>121</v>
       </c>
-      <c r="F30" s="23"/>
+      <c r="F30" s="27"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
@@ -4319,7 +4827,7 @@
       <c r="E31" t="s">
         <v>325</v>
       </c>
-      <c r="F31" s="23"/>
+      <c r="F31" s="27"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
@@ -4335,7 +4843,7 @@
       <c r="E32" t="s">
         <v>325</v>
       </c>
-      <c r="F32" s="23"/>
+      <c r="F32" s="27"/>
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
@@ -4350,7 +4858,7 @@
       <c r="D33" t="s">
         <v>123</v>
       </c>
-      <c r="F33" s="23"/>
+      <c r="F33" s="27"/>
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
@@ -4365,7 +4873,7 @@
       <c r="D34" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="23"/>
+      <c r="F34" s="27"/>
     </row>
     <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -4380,7 +4888,7 @@
       <c r="D35" t="s">
         <v>120</v>
       </c>
-      <c r="F35" s="23"/>
+      <c r="F35" s="27"/>
     </row>
     <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
@@ -4395,7 +4903,7 @@
       <c r="D36" t="s">
         <v>121</v>
       </c>
-      <c r="F36" s="23"/>
+      <c r="F36" s="27"/>
     </row>
     <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -4410,7 +4918,7 @@
       <c r="D37" t="s">
         <v>121</v>
       </c>
-      <c r="F37" s="23"/>
+      <c r="F37" s="27"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -4426,7 +4934,7 @@
       <c r="E38" t="s">
         <v>325</v>
       </c>
-      <c r="F38" s="23"/>
+      <c r="F38" s="27"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
@@ -4442,7 +4950,7 @@
       <c r="E39" t="s">
         <v>325</v>
       </c>
-      <c r="F39" s="23"/>
+      <c r="F39" s="27"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
@@ -4458,7 +4966,7 @@
       <c r="E40" t="s">
         <v>325</v>
       </c>
-      <c r="F40" s="23"/>
+      <c r="F40" s="27"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
@@ -4474,7 +4982,7 @@
       <c r="E41" t="s">
         <v>325</v>
       </c>
-      <c r="F41" s="23"/>
+      <c r="F41" s="27"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
@@ -4490,7 +4998,7 @@
       <c r="E42" t="s">
         <v>325</v>
       </c>
-      <c r="F42" s="23"/>
+      <c r="F42" s="27"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
@@ -4506,7 +5014,7 @@
       <c r="E43" t="s">
         <v>325</v>
       </c>
-      <c r="F43" s="23"/>
+      <c r="F43" s="27"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
@@ -4522,7 +5030,7 @@
       <c r="E44" t="s">
         <v>325</v>
       </c>
-      <c r="F44" s="23"/>
+      <c r="F44" s="27"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
@@ -4538,7 +5046,7 @@
       <c r="E45" t="s">
         <v>325</v>
       </c>
-      <c r="F45" s="23"/>
+      <c r="F45" s="27"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
@@ -4554,7 +5062,7 @@
       <c r="E46" t="s">
         <v>325</v>
       </c>
-      <c r="F46" s="23"/>
+      <c r="F46" s="27"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
@@ -4570,7 +5078,7 @@
       <c r="E47" t="s">
         <v>325</v>
       </c>
-      <c r="F47" s="23"/>
+      <c r="F47" s="27"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
@@ -4591,7 +5099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F40370-0450-354F-8050-D882F7C6B124}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4605,14 +5113,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -4642,7 +5150,7 @@
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="25" t="s">
         <v>133</v>
       </c>
     </row>
@@ -4662,7 +5170,7 @@
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="21"/>
+      <c r="F4" s="25"/>
     </row>
     <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -4680,7 +5188,7 @@
       <c r="E5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="21"/>
+      <c r="F5" s="25"/>
     </row>
     <row r="6" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -4698,7 +5206,7 @@
       <c r="E6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="21"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -4716,7 +5224,7 @@
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="21"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -4734,7 +5242,7 @@
       <c r="E8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="21"/>
+      <c r="F8" s="25"/>
     </row>
     <row r="9" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -4752,7 +5260,7 @@
       <c r="E9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="21"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -4770,7 +5278,7 @@
       <c r="E10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="21"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -4788,7 +5296,7 @@
       <c r="E11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="21"/>
+      <c r="F11" s="25"/>
     </row>
     <row r="12" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -4806,7 +5314,7 @@
       <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="21"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
@@ -4816,7 +5324,7 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="21"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -4834,7 +5342,7 @@
       <c r="E14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="21"/>
+      <c r="F14" s="25"/>
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -4852,7 +5360,7 @@
       <c r="E15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="21"/>
+      <c r="F15" s="25"/>
     </row>
     <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -4870,7 +5378,7 @@
       <c r="E16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="21"/>
+      <c r="F16" s="25"/>
     </row>
     <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -4888,7 +5396,7 @@
       <c r="E17" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="21"/>
+      <c r="F17" s="25"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F18" s="18"/>
@@ -4933,7 +5441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A858ECB-AA45-354B-B7AC-CA760D10B01A}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4948,13 +5456,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>372</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -4997,7 +5505,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -5018,7 +5526,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="23"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -5037,7 +5545,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="7"/>
-      <c r="G5" s="23"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -5056,7 +5564,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="7"/>
-      <c r="G6" s="23"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -5075,7 +5583,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="7"/>
-      <c r="G7" s="23"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -5094,7 +5602,7 @@
         <v>37</v>
       </c>
       <c r="F8" s="7"/>
-      <c r="G8" s="23"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -5113,7 +5621,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="7"/>
-      <c r="G9" s="23"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -5132,7 +5640,7 @@
         <v>36</v>
       </c>
       <c r="F10" s="7"/>
-      <c r="G10" s="23"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -5151,7 +5659,7 @@
         <v>353</v>
       </c>
       <c r="F11" s="7"/>
-      <c r="G11" s="23"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -5170,7 +5678,7 @@
         <v>170</v>
       </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="23"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -5189,7 +5697,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="7"/>
-      <c r="G13" s="23"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5201,8 +5709,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="28" t="s">
         <v>485</v>
       </c>
     </row>
@@ -5217,7 +5725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B1D3717-B579-8144-B029-DF32844FBBBF}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5230,13 +5738,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -5275,7 +5783,7 @@
       <c r="E3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -5295,7 +5803,7 @@
       <c r="E4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -5313,7 +5821,7 @@
       <c r="E5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -5331,7 +5839,7 @@
       <c r="E6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="272" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -5349,7 +5857,7 @@
       <c r="E7" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -5364,7 +5872,7 @@
       <c r="E8" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -5382,7 +5890,7 @@
       <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="176" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -5400,7 +5908,7 @@
       <c r="E10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -5411,13 +5919,13 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="29" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="28" t="s">
         <v>486</v>
       </c>
     </row>
@@ -5436,7 +5944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDE2540-0ACF-7B44-83F9-21CF88C021C7}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5449,13 +5957,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -5494,7 +6002,7 @@
       <c r="E3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -5514,7 +6022,7 @@
       <c r="E4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -5532,7 +6040,7 @@
       <c r="E5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -5550,7 +6058,7 @@
       <c r="E6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -5568,7 +6076,7 @@
       <c r="E7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -5586,7 +6094,7 @@
       <c r="E8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="96" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -5604,7 +6112,7 @@
       <c r="E9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="144" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -5622,7 +6130,7 @@
       <c r="E10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -5640,7 +6148,7 @@
       <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -5656,8 +6164,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="28" t="s">
         <v>486</v>
       </c>
     </row>
@@ -5666,328 +6174,6 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F3:F11"/>
     <mergeCell ref="A15:XFD15"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D95401-61D3-9745-9918-08171A199350}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="25.1640625" customWidth="1"/>
-    <col min="2" max="2" width="52.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="16" style="7" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>369</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="21" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="21"/>
-    </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="21"/>
-    </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="21"/>
-    </row>
-    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="21"/>
-    </row>
-    <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="21"/>
-    </row>
-    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="21"/>
-    </row>
-    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="21"/>
-    </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="21"/>
-    </row>
-    <row r="12" spans="1:6" ht="64" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="21"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="21"/>
-    </row>
-    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="21"/>
-    </row>
-    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="21"/>
-    </row>
-    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="21"/>
-    </row>
-    <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="21"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F18" s="18"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>134</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F3:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
@@ -6008,14 +6194,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -6045,7 +6231,7 @@
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="25" t="s">
         <v>133</v>
       </c>
     </row>
@@ -6065,7 +6251,7 @@
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="21"/>
+      <c r="F4" s="25"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -6083,7 +6269,7 @@
       <c r="E5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="21"/>
+      <c r="F5" s="25"/>
     </row>
     <row r="6" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -6101,7 +6287,7 @@
       <c r="E6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="21"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -6119,7 +6305,7 @@
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="21"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -6137,7 +6323,7 @@
       <c r="E8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="21"/>
+      <c r="F8" s="25"/>
     </row>
     <row r="9" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -6155,7 +6341,7 @@
       <c r="E9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="21"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -6173,7 +6359,7 @@
       <c r="E10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="21"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -6191,7 +6377,7 @@
       <c r="E11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="21"/>
+      <c r="F11" s="25"/>
     </row>
     <row r="12" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -6209,7 +6395,7 @@
       <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="21"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
@@ -6219,7 +6405,7 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="21"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -6237,7 +6423,7 @@
       <c r="E14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="21"/>
+      <c r="F14" s="25"/>
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -6255,7 +6441,7 @@
       <c r="E15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="21"/>
+      <c r="F15" s="25"/>
     </row>
     <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -6273,7 +6459,7 @@
       <c r="E16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="21"/>
+      <c r="F16" s="25"/>
     </row>
     <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -6291,7 +6477,7 @@
       <c r="E17" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="21"/>
+      <c r="F17" s="25"/>
     </row>
     <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="8"/>
@@ -6319,6 +6505,328 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D95401-61D3-9745-9918-08171A199350}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25"/>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25"/>
+    </row>
+    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="25"/>
+    </row>
+    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="25"/>
+    </row>
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="25"/>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25"/>
+    </row>
+    <row r="12" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="25"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="25"/>
+    </row>
+    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="25"/>
+    </row>
+    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="25"/>
+    </row>
+    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="25"/>
+    </row>
+    <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="25"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F18" s="18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="F3:F17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1610996-D53A-164B-AD18-8A6464F889A3}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -6333,13 +6841,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -6382,7 +6890,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -6403,7 +6911,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="23"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -6422,7 +6930,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="7"/>
-      <c r="G5" s="23"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -6441,7 +6949,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="7"/>
-      <c r="G6" s="23"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -6460,7 +6968,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="7"/>
-      <c r="G7" s="23"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -6479,7 +6987,7 @@
         <v>37</v>
       </c>
       <c r="F8" s="7"/>
-      <c r="G8" s="23"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -6498,7 +7006,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="7"/>
-      <c r="G9" s="23"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -6517,7 +7025,7 @@
         <v>36</v>
       </c>
       <c r="F10" s="7"/>
-      <c r="G10" s="23"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -6536,7 +7044,7 @@
         <v>353</v>
       </c>
       <c r="F11" s="7"/>
-      <c r="G11" s="23"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -6555,7 +7063,7 @@
         <v>170</v>
       </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="23"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -6574,7 +7082,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="7"/>
-      <c r="G13" s="23"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -6586,8 +7094,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="28" t="s">
         <v>485</v>
       </c>
     </row>
@@ -6602,7 +7110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D596A14E-EAFE-FD42-A021-8756D4834C88}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -6614,13 +7122,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -6659,7 +7167,7 @@
       <c r="E3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -6679,7 +7187,7 @@
       <c r="E4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -6697,7 +7205,7 @@
       <c r="E5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -6715,7 +7223,7 @@
       <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -6733,7 +7241,7 @@
       <c r="E7" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -6748,7 +7256,7 @@
       <c r="D8" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -6766,7 +7274,7 @@
       <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -6784,7 +7292,7 @@
       <c r="E10" t="s">
         <v>403</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -6802,11 +7310,11 @@
       <c r="E11" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D12" s="8"/>
-      <c r="F12" s="23"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -6828,7 +7336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{918F2BE0-8FD4-784B-B085-44FF2420D596}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -6841,13 +7349,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>420</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -6886,7 +7394,7 @@
       <c r="E3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -6906,7 +7414,7 @@
       <c r="E4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -6924,7 +7432,7 @@
       <c r="E5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -6942,7 +7450,7 @@
       <c r="E6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="365" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -6960,7 +7468,7 @@
       <c r="E7" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -6975,7 +7483,7 @@
       <c r="E8" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -6993,7 +7501,7 @@
       <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -7011,7 +7519,7 @@
       <c r="E10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -7022,13 +7530,13 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="29" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="28" t="s">
         <v>486</v>
       </c>
     </row>
@@ -7047,7 +7555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F532CB-00F4-1C49-9643-BC3D72AFCE2D}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -7060,13 +7568,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>419</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -7105,7 +7613,7 @@
       <c r="E3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7125,7 +7633,7 @@
       <c r="E4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -7143,7 +7651,7 @@
       <c r="E5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -7161,7 +7669,7 @@
       <c r="E6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -7179,7 +7687,7 @@
       <c r="E7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -7197,7 +7705,7 @@
       <c r="E8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -7215,7 +7723,7 @@
       <c r="E9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -7233,7 +7741,7 @@
       <c r="E10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -7251,7 +7759,7 @@
       <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -7267,8 +7775,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="28" t="s">
         <v>486</v>
       </c>
     </row>
@@ -7283,7 +7791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39719259-CABC-7944-B796-3CF001A852C6}">
   <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -7297,13 +7805,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -7339,7 +7847,7 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7356,7 +7864,7 @@
       <c r="D4" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -7371,7 +7879,7 @@
       <c r="D5" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -7386,7 +7894,7 @@
       <c r="D6" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -7401,7 +7909,7 @@
       <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -7416,7 +7924,7 @@
       <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -7431,7 +7939,7 @@
       <c r="D9" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -7446,7 +7954,7 @@
       <c r="D10" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -7462,7 +7970,7 @@
       <c r="E11" t="s">
         <v>459</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -7477,7 +7985,7 @@
       <c r="D12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="23"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -7492,7 +8000,7 @@
       <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="23"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -7507,7 +8015,7 @@
       <c r="D14" t="s">
         <v>120</v>
       </c>
-      <c r="F14" s="23"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -7523,7 +8031,7 @@
       <c r="E15" t="s">
         <v>459</v>
       </c>
-      <c r="F15" s="23"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -7539,7 +8047,7 @@
       <c r="E16" t="s">
         <v>459</v>
       </c>
-      <c r="F16" s="23"/>
+      <c r="F16" s="27"/>
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -7554,7 +8062,7 @@
       <c r="D17" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="23"/>
+      <c r="F17" s="27"/>
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
@@ -7569,7 +8077,7 @@
       <c r="D18" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="23"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
@@ -7584,7 +8092,7 @@
       <c r="D19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="23"/>
+      <c r="F19" s="27"/>
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
@@ -7599,7 +8107,7 @@
       <c r="D20" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="23"/>
+      <c r="F20" s="27"/>
     </row>
     <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
@@ -7614,7 +8122,7 @@
       <c r="D21" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="23"/>
+      <c r="F21" s="27"/>
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
@@ -7629,7 +8137,7 @@
       <c r="D22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="23"/>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -7645,7 +8153,7 @@
       <c r="E23" t="s">
         <v>459</v>
       </c>
-      <c r="F23" s="23"/>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
@@ -7660,7 +8168,7 @@
       <c r="D24" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="23"/>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
@@ -7675,7 +8183,7 @@
       <c r="D25" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="23"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
@@ -7690,7 +8198,7 @@
       <c r="D26" t="s">
         <v>121</v>
       </c>
-      <c r="F26" s="23"/>
+      <c r="F26" s="27"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
@@ -7706,7 +8214,7 @@
       <c r="E27" t="s">
         <v>459</v>
       </c>
-      <c r="F27" s="23"/>
+      <c r="F27" s="27"/>
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
@@ -7721,7 +8229,7 @@
       <c r="D28" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="23"/>
+      <c r="F28" s="27"/>
     </row>
     <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -7736,7 +8244,7 @@
       <c r="D29" t="s">
         <v>120</v>
       </c>
-      <c r="F29" s="23"/>
+      <c r="F29" s="27"/>
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
@@ -7751,7 +8259,7 @@
       <c r="D30" t="s">
         <v>121</v>
       </c>
-      <c r="F30" s="23"/>
+      <c r="F30" s="27"/>
     </row>
     <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
@@ -7766,7 +8274,7 @@
       <c r="D31" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="23"/>
+      <c r="F31" s="27"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
@@ -7782,7 +8290,7 @@
       <c r="E32" t="s">
         <v>459</v>
       </c>
-      <c r="F32" s="23"/>
+      <c r="F32" s="27"/>
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
@@ -7797,7 +8305,7 @@
       <c r="D33" t="s">
         <v>123</v>
       </c>
-      <c r="F33" s="23"/>
+      <c r="F33" s="27"/>
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
@@ -7812,7 +8320,7 @@
       <c r="D34" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="23"/>
+      <c r="F34" s="27"/>
     </row>
     <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -7827,7 +8335,7 @@
       <c r="D35" t="s">
         <v>120</v>
       </c>
-      <c r="F35" s="23"/>
+      <c r="F35" s="27"/>
     </row>
     <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
@@ -7842,7 +8350,7 @@
       <c r="D36" t="s">
         <v>121</v>
       </c>
-      <c r="F36" s="23"/>
+      <c r="F36" s="27"/>
     </row>
     <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -7857,7 +8365,7 @@
       <c r="D37" t="s">
         <v>121</v>
       </c>
-      <c r="F37" s="23"/>
+      <c r="F37" s="27"/>
     </row>
     <row r="38" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -7872,7 +8380,7 @@
       <c r="D38" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="23"/>
+      <c r="F38" s="27"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
@@ -7888,7 +8396,7 @@
       <c r="E39" t="s">
         <v>459</v>
       </c>
-      <c r="F39" s="23"/>
+      <c r="F39" s="27"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
@@ -7904,7 +8412,7 @@
       <c r="E40" t="s">
         <v>459</v>
       </c>
-      <c r="F40" s="23"/>
+      <c r="F40" s="27"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
@@ -7920,7 +8428,7 @@
       <c r="E41" t="s">
         <v>459</v>
       </c>
-      <c r="F41" s="23"/>
+      <c r="F41" s="27"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
@@ -7936,7 +8444,7 @@
       <c r="E42" t="s">
         <v>459</v>
       </c>
-      <c r="F42" s="23"/>
+      <c r="F42" s="27"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
@@ -7952,7 +8460,7 @@
       <c r="E43" t="s">
         <v>459</v>
       </c>
-      <c r="F43" s="23"/>
+      <c r="F43" s="27"/>
     </row>
     <row r="44" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
@@ -7967,7 +8475,7 @@
       <c r="D44" t="s">
         <v>121</v>
       </c>
-      <c r="F44" s="23"/>
+      <c r="F44" s="27"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
@@ -7983,7 +8491,7 @@
       <c r="E45" t="s">
         <v>459</v>
       </c>
-      <c r="F45" s="23"/>
+      <c r="F45" s="27"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
@@ -7999,7 +8507,7 @@
       <c r="E46" t="s">
         <v>459</v>
       </c>
-      <c r="F46" s="23"/>
+      <c r="F46" s="27"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
@@ -8015,7 +8523,7 @@
       <c r="E47" t="s">
         <v>459</v>
       </c>
-      <c r="F47" s="23"/>
+      <c r="F47" s="27"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
@@ -8052,13 +8560,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -8101,7 +8609,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -8122,7 +8630,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="23"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -8141,7 +8649,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="7"/>
-      <c r="G5" s="23"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -8160,7 +8668,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="7"/>
-      <c r="G6" s="23"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -8179,7 +8687,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="7"/>
-      <c r="G7" s="23"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -8198,7 +8706,7 @@
         <v>37</v>
       </c>
       <c r="F8" s="7"/>
-      <c r="G8" s="23"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -8217,7 +8725,7 @@
         <v>462</v>
       </c>
       <c r="F9" s="7"/>
-      <c r="G9" s="23"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -8236,7 +8744,7 @@
         <v>36</v>
       </c>
       <c r="F10" s="7"/>
-      <c r="G10" s="23"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -8247,7 +8755,7 @@
       <c r="F11" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="G11" s="23"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -8266,7 +8774,7 @@
         <v>170</v>
       </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="23"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -8285,7 +8793,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="7"/>
-      <c r="G13" s="23"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -8297,8 +8805,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="28" t="s">
         <v>485</v>
       </c>
     </row>
@@ -8327,13 +8835,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -8372,7 +8880,7 @@
       <c r="E3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -8392,7 +8900,7 @@
       <c r="E4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -8410,7 +8918,7 @@
       <c r="E5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -8428,7 +8936,7 @@
       <c r="E6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="256" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -8446,7 +8954,7 @@
       <c r="E7" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -8461,7 +8969,7 @@
       <c r="E8" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -8479,7 +8987,7 @@
       <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -8497,7 +9005,7 @@
       <c r="E10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -8508,13 +9016,13 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="29" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="28" t="s">
         <v>486</v>
       </c>
     </row>
@@ -8548,12 +9056,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>473</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="17"/>
       <c r="F1" s="7"/>
     </row>
@@ -8766,8 +9274,8 @@
       </c>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:6" s="26" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="26" t="s">
+    <row r="15" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="30" t="s">
         <v>469</v>
       </c>
     </row>
@@ -8777,7 +9285,7 @@
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" s="26" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="17" s="30" customFormat="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A15:XFD15"/>
@@ -8807,13 +9315,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -8852,7 +9360,7 @@
       <c r="E3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -8872,7 +9380,7 @@
       <c r="E4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -8890,7 +9398,7 @@
       <c r="E5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -8908,7 +9416,7 @@
       <c r="E6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -8926,7 +9434,7 @@
       <c r="E7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -8944,7 +9452,7 @@
       <c r="E8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -8962,7 +9470,7 @@
       <c r="E9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="96" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -8980,7 +9488,7 @@
       <c r="E10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -8998,7 +9506,7 @@
       <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -9014,8 +9522,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="28" t="s">
         <v>486</v>
       </c>
     </row>
@@ -9048,13 +9556,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -9093,7 +9601,7 @@
       <c r="E3" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>474</v>
       </c>
     </row>
@@ -9113,7 +9621,7 @@
       <c r="E4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
@@ -9131,7 +9639,7 @@
       <c r="E5" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
@@ -9149,7 +9657,7 @@
       <c r="E6" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -9167,7 +9675,7 @@
       <c r="E7" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
@@ -9185,7 +9693,7 @@
       <c r="E8" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="80" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -9203,7 +9711,7 @@
       <c r="E9" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
@@ -9221,7 +9729,7 @@
       <c r="E10" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
@@ -9239,7 +9747,7 @@
       <c r="E11" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -9257,7 +9765,7 @@
       <c r="E12" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="23"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
@@ -9275,7 +9783,7 @@
       <c r="E13" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F13" s="23"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="8"/>
@@ -9286,8 +9794,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27" t="s">
+    <row r="16" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="31" t="s">
         <v>136</v>
       </c>
     </row>
@@ -9319,13 +9827,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -9361,7 +9869,7 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -9378,7 +9886,7 @@
       <c r="D4" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -9393,7 +9901,7 @@
       <c r="D5" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -9408,7 +9916,7 @@
       <c r="D6" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -9423,7 +9931,7 @@
       <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="23"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -9438,7 +9946,7 @@
       <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -9453,7 +9961,7 @@
       <c r="D9" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -9468,7 +9976,7 @@
       <c r="D10" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -9484,7 +9992,7 @@
       <c r="E11" t="s">
         <v>231</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -9499,7 +10007,7 @@
       <c r="D12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="23"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -9514,7 +10022,7 @@
       <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="23"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -9529,7 +10037,7 @@
       <c r="D14" t="s">
         <v>120</v>
       </c>
-      <c r="F14" s="23"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -9547,7 +10055,7 @@
       <c r="E15" t="s">
         <v>500</v>
       </c>
-      <c r="F15" s="23"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -9565,7 +10073,7 @@
       <c r="E16" t="s">
         <v>500</v>
       </c>
-      <c r="F16" s="23"/>
+      <c r="F16" s="27"/>
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -9580,7 +10088,7 @@
       <c r="D17" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="23"/>
+      <c r="F17" s="27"/>
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
@@ -9595,7 +10103,7 @@
       <c r="D18" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="23"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
@@ -9610,7 +10118,7 @@
       <c r="D19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="23"/>
+      <c r="F19" s="27"/>
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
@@ -9625,7 +10133,7 @@
       <c r="D20" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="23"/>
+      <c r="F20" s="27"/>
     </row>
     <row r="21" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
@@ -9640,7 +10148,7 @@
       <c r="D21" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="23"/>
+      <c r="F21" s="27"/>
     </row>
     <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
@@ -9655,7 +10163,7 @@
       <c r="D22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="23"/>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -9673,7 +10181,7 @@
       <c r="E23" t="s">
         <v>500</v>
       </c>
-      <c r="F23" s="23"/>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
@@ -9688,7 +10196,7 @@
       <c r="D24" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="23"/>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
@@ -9703,7 +10211,7 @@
       <c r="D25" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="23"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
@@ -9718,7 +10226,7 @@
       <c r="D26" t="s">
         <v>121</v>
       </c>
-      <c r="F26" s="23"/>
+      <c r="F26" s="27"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
@@ -9734,7 +10242,7 @@
       <c r="E27" t="s">
         <v>231</v>
       </c>
-      <c r="F27" s="23"/>
+      <c r="F27" s="27"/>
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
@@ -9749,7 +10257,7 @@
       <c r="D28" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="23"/>
+      <c r="F28" s="27"/>
     </row>
     <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -9764,7 +10272,7 @@
       <c r="D29" t="s">
         <v>120</v>
       </c>
-      <c r="F29" s="23"/>
+      <c r="F29" s="27"/>
     </row>
     <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
@@ -9779,7 +10287,7 @@
       <c r="D30" t="s">
         <v>121</v>
       </c>
-      <c r="F30" s="23"/>
+      <c r="F30" s="27"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
@@ -9795,7 +10303,7 @@
       <c r="E31" t="s">
         <v>231</v>
       </c>
-      <c r="F31" s="23"/>
+      <c r="F31" s="27"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
@@ -9811,7 +10319,7 @@
       <c r="E32" t="s">
         <v>231</v>
       </c>
-      <c r="F32" s="23"/>
+      <c r="F32" s="27"/>
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
@@ -9826,7 +10334,7 @@
       <c r="D33" t="s">
         <v>123</v>
       </c>
-      <c r="F33" s="23"/>
+      <c r="F33" s="27"/>
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
@@ -9841,7 +10349,7 @@
       <c r="D34" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="23"/>
+      <c r="F34" s="27"/>
     </row>
     <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -9856,7 +10364,7 @@
       <c r="D35" t="s">
         <v>120</v>
       </c>
-      <c r="F35" s="23"/>
+      <c r="F35" s="27"/>
     </row>
     <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
@@ -9871,7 +10379,7 @@
       <c r="D36" t="s">
         <v>121</v>
       </c>
-      <c r="F36" s="23"/>
+      <c r="F36" s="27"/>
     </row>
     <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -9886,7 +10394,7 @@
       <c r="D37" t="s">
         <v>121</v>
       </c>
-      <c r="F37" s="23"/>
+      <c r="F37" s="27"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -9902,7 +10410,7 @@
       <c r="E38" t="s">
         <v>231</v>
       </c>
-      <c r="F38" s="23"/>
+      <c r="F38" s="27"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
@@ -9920,7 +10428,7 @@
       <c r="E39" t="s">
         <v>501</v>
       </c>
-      <c r="F39" s="23"/>
+      <c r="F39" s="27"/>
     </row>
     <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
@@ -9938,7 +10446,7 @@
       <c r="E40" t="s">
         <v>501</v>
       </c>
-      <c r="F40" s="23"/>
+      <c r="F40" s="27"/>
     </row>
     <row r="41" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
@@ -9956,7 +10464,7 @@
       <c r="E41" t="s">
         <v>501</v>
       </c>
-      <c r="F41" s="23"/>
+      <c r="F41" s="27"/>
     </row>
     <row r="42" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
@@ -9974,7 +10482,7 @@
       <c r="E42" t="s">
         <v>501</v>
       </c>
-      <c r="F42" s="23"/>
+      <c r="F42" s="27"/>
     </row>
     <row r="43" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
@@ -9992,7 +10500,7 @@
       <c r="E43" t="s">
         <v>501</v>
       </c>
-      <c r="F43" s="23"/>
+      <c r="F43" s="27"/>
     </row>
     <row r="44" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
@@ -10010,7 +10518,7 @@
       <c r="E44" t="s">
         <v>501</v>
       </c>
-      <c r="F44" s="23"/>
+      <c r="F44" s="27"/>
     </row>
     <row r="45" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
@@ -10028,7 +10536,7 @@
       <c r="E45" t="s">
         <v>500</v>
       </c>
-      <c r="F45" s="23"/>
+      <c r="F45" s="27"/>
     </row>
     <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
@@ -10046,7 +10554,7 @@
       <c r="E46" t="s">
         <v>500</v>
       </c>
-      <c r="F46" s="23"/>
+      <c r="F46" s="27"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
@@ -10062,7 +10570,7 @@
       <c r="E47" t="s">
         <v>231</v>
       </c>
-      <c r="F47" s="23"/>
+      <c r="F47" s="27"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
@@ -10087,325 +10595,289 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21D5B17-DF60-214C-A0BB-8AA9F6288E63}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF4BED80-62E4-DB4A-9AD1-A06EA450D158}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.1640625" customWidth="1"/>
-    <col min="2" max="2" width="52.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="16" style="7" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="56.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="44.83203125" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>484</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="B1" s="24" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
+        <v>522</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="21" t="s">
+        <v>502</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>405</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="21" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="21"/>
-    </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="21"/>
-    </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="21"/>
-    </row>
-    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="21"/>
-    </row>
-    <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="21"/>
-    </row>
-    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="21"/>
-    </row>
-    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="21"/>
-    </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="21"/>
-    </row>
-    <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="21"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="21"/>
-    </row>
-    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="21"/>
-    </row>
-    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="21"/>
-    </row>
-    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="21"/>
-    </row>
-    <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="21"/>
-    </row>
-    <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>134</v>
+    </row>
+    <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3" s="22">
+        <v>63105010</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>504</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>504</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
+        <v>524</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A6" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A7" s="22" t="s">
+        <v>527</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="19" x14ac:dyDescent="0.2">
+      <c r="A8" s="22" t="s">
+        <v>529</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>537</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A10" s="22" t="s">
+        <v>535</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A11" s="22" t="s">
+        <v>530</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>512</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="A12" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>514</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A13" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>538</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="A14" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>539</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="38" x14ac:dyDescent="0.2">
+      <c r="A15" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>533</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="38" x14ac:dyDescent="0.2">
+      <c r="A16" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>520</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>532</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A18" s="33" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A19" s="33" t="s">
+        <v>541</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F3:F17"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
 </worksheet>
 </file>